--- a/raw/processedSamples/20260519_r13_CMH_USDA-blood_Nano-QuIC.xlsx
+++ b/raw/processedSamples/20260519_r13_CMH_USDA-blood_Nano-QuIC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F16A9CF-43B0-45E0-851C-66353E54AEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEB4458-0B92-4C1F-ABCC-9FC06A521D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F8DBAC4F-C712-4491-AA09-EB5717C4C264}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F8DBAC4F-C712-4491-AA09-EB5717C4C264}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Time 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -778,7 +778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -835,6 +835,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -88527,298 +88530,298 @@
         <v>596</v>
       </c>
     </row>
-    <row r="302" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A302" s="2" t="s">
+    <row r="302" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A302" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B302" s="3"/>
-      <c r="C302" s="4">
+      <c r="C302" s="5">
         <v>1000</v>
       </c>
-      <c r="D302" s="4">
-        <v>100</v>
-      </c>
-      <c r="E302" s="4">
-        <v>100</v>
-      </c>
-      <c r="F302" s="4">
-        <v>100</v>
-      </c>
-      <c r="G302" s="4">
-        <v>100</v>
-      </c>
-      <c r="H302" s="4">
-        <v>100</v>
-      </c>
-      <c r="I302" s="4">
-        <v>100</v>
-      </c>
-      <c r="J302" s="4">
-        <v>100</v>
-      </c>
-      <c r="K302" s="4">
-        <v>100</v>
-      </c>
-      <c r="L302" s="4">
-        <v>100</v>
-      </c>
-      <c r="M302" s="4">
-        <v>100</v>
-      </c>
-      <c r="N302" s="4">
-        <v>100</v>
-      </c>
-      <c r="O302" s="4">
+      <c r="D302" s="12">
+        <v>4</v>
+      </c>
+      <c r="E302" s="12">
+        <v>4</v>
+      </c>
+      <c r="F302" s="12">
+        <v>4</v>
+      </c>
+      <c r="G302" s="12">
+        <v>4</v>
+      </c>
+      <c r="H302" s="12">
+        <v>4</v>
+      </c>
+      <c r="I302" s="12">
+        <v>4</v>
+      </c>
+      <c r="J302" s="12">
+        <v>4</v>
+      </c>
+      <c r="K302" s="12">
+        <v>4</v>
+      </c>
+      <c r="L302" s="12">
+        <v>4</v>
+      </c>
+      <c r="M302" s="12">
+        <v>4</v>
+      </c>
+      <c r="N302" s="12">
+        <v>4</v>
+      </c>
+      <c r="O302" s="5">
         <v>1000</v>
       </c>
-      <c r="P302" s="4">
-        <v>100</v>
-      </c>
-      <c r="Q302" s="4">
-        <v>100</v>
-      </c>
-      <c r="R302" s="4">
-        <v>100</v>
-      </c>
-      <c r="S302" s="4">
-        <v>100</v>
-      </c>
-      <c r="T302" s="4">
-        <v>100</v>
-      </c>
-      <c r="U302" s="4">
-        <v>100</v>
-      </c>
-      <c r="V302" s="4">
-        <v>100</v>
-      </c>
-      <c r="W302" s="4">
-        <v>100</v>
-      </c>
-      <c r="X302" s="4">
-        <v>100</v>
-      </c>
-      <c r="Y302" s="4">
-        <v>100</v>
-      </c>
-      <c r="Z302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AA302" s="4">
+      <c r="P302" s="12">
+        <v>4</v>
+      </c>
+      <c r="Q302" s="12">
+        <v>4</v>
+      </c>
+      <c r="R302" s="12">
+        <v>4</v>
+      </c>
+      <c r="S302" s="12">
+        <v>4</v>
+      </c>
+      <c r="T302" s="12">
+        <v>4</v>
+      </c>
+      <c r="U302" s="12">
+        <v>4</v>
+      </c>
+      <c r="V302" s="12">
+        <v>4</v>
+      </c>
+      <c r="W302" s="12">
+        <v>4</v>
+      </c>
+      <c r="X302" s="12">
+        <v>4</v>
+      </c>
+      <c r="Y302" s="12">
+        <v>4</v>
+      </c>
+      <c r="Z302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AA302" s="5">
         <v>1000</v>
       </c>
-      <c r="AB302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AC302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AD302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AE302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AF302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AG302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AH302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AI302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AJ302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AK302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AL302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AM302" s="4">
+      <c r="AB302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AC302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AD302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AE302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AF302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AG302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AH302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AI302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AJ302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AK302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AL302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AM302" s="5">
         <v>1000</v>
       </c>
-      <c r="AN302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AO302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AP302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AQ302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AR302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AS302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AU302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AV302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AW302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AX302" s="4">
-        <v>100</v>
-      </c>
-      <c r="AY302" s="4">
+      <c r="AN302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AO302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AP302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AQ302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AR302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AS302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AT302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AU302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AV302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AW302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AX302" s="12">
+        <v>4</v>
+      </c>
+      <c r="AY302" s="5">
         <v>1000</v>
       </c>
-      <c r="AZ302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BA302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BB302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BC302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BD302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BE302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BF302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BG302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BH302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BI302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BJ302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BK302" s="4">
+      <c r="AZ302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BA302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BB302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BC302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BD302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BE302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BF302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BG302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BH302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BI302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BJ302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BK302" s="5">
         <v>1000</v>
       </c>
-      <c r="BL302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BM302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BN302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BO302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BP302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BQ302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BR302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BS302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BT302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BU302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BV302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BW302" s="4">
+      <c r="BL302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BM302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BN302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BO302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BP302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BQ302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BR302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BS302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BT302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BU302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BV302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BW302" s="5">
         <v>1000</v>
       </c>
-      <c r="BX302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BY302" s="4">
-        <v>100</v>
-      </c>
-      <c r="BZ302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CA302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CB302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CC302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CD302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CE302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CF302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CG302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CH302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CI302" s="4">
+      <c r="BX302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BY302" s="12">
+        <v>4</v>
+      </c>
+      <c r="BZ302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CA302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CB302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CC302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CD302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CE302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CF302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CG302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CH302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CI302" s="5">
         <v>1000</v>
       </c>
-      <c r="CJ302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CK302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CL302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CM302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CN302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CO302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CP302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CQ302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CR302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CS302" s="4">
-        <v>100</v>
-      </c>
-      <c r="CT302" s="5">
-        <v>100</v>
+      <c r="CJ302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CK302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CL302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CM302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CN302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CO302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CP302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CQ302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CR302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CS302" s="12">
+        <v>4</v>
+      </c>
+      <c r="CT302" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:98" ht="30" x14ac:dyDescent="0.25">
